--- a/data/ct_scoop/ct_scoop_links_2026-05-07.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-05-07.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,103 +440,178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MANSFIELD SCOOP: Dad's Doughs closing Mansfield doughnut shop</t>
+          <t>MANCHESTER SCOOP: 2nd Bridge Soccer Pub &amp; Brewery reopens after renovations!</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/mansfield-scoop-dads-doughs-closing-mansfield-doughnut-shop</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-2nd-bridge-soccer-pub-brewery-reopens-after-renovations</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WEST HARTFORD SCOOP: New matcha &amp; dessert shop coming to WeHa</t>
+          <t>MILFORD SCOOP: New coffee shop coming to former Subway space</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-new-matcha-dessert-shop-coming-to-weha</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-new-coffee-shop-coming-to-former-subway-space</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHESHIRE SCOOP: Seafood &amp; Steakhosue coming to The Shops at Stone Bridge!</t>
+          <t>BRIDGEPORT SCOOP: Juici Patties bring first CT location in Bridgeport</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-seafood-steakhosue-coming-to-the-shops-at-stone-bridge</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/bridgeport-scoop-juici-patties-bring-first-ct-location-in-bridgeport</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EAST LONGMEADOW SCOOP: Two new restaurants proposed in East Longmeadow!</t>
+          <t>HOLYOKE SCOOP:  Chick-Fil-A comes to Holyoke Mall!</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-mass-posts/east-longmeadow-scoop-two-new-restaurants-proposed-in-east-longmeadow</t>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/holyoke-scoop-chick-fil-a-comes-to-holyoke-mall</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEWINGTON SCOOP: Ross Dress for Less officially coming to Newington, Plaza receives new name!</t>
+          <t>FOXBOROUGH SCOOP: New kid's entertainment center coming to Patriot Place!</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-ross-dress-for-less-officially-coming-to-newington-plaza-receives-new-name</t>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/foxborough-scoop-new-kids-entertainment-center-coming-to-patriot-place</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WATERBURY SCOOP: New restaurant coming soon to Chase Avenue</t>
+          <t>MANSFIELD SCOOP: Dad's Doughs closing Mansfield doughnut shop</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/waterbury-scoop-new-restaurant-coming-soon-to-chase-avenue</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/mansfield-scoop-dads-doughs-closing-mansfield-doughnut-shop</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>WEST HARTFORD SCOOP: New matcha &amp; dessert shop coming to WeHa</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-new-matcha-dessert-shop-coming-to-weha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHESHIRE SCOOP: Seafood &amp; Steakhosue coming to The Shops at Stone Bridge!</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-seafood-steakhosue-coming-to-the-shops-at-stone-bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EAST LONGMEADOW SCOOP: Two new restaurants proposed in East Longmeadow!</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/east-longmeadow-scoop-two-new-restaurants-proposed-in-east-longmeadow</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEWINGTON SCOOP: Ross Dress for Less officially coming to Newington, Plaza receives new name!</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-ross-dress-for-less-officially-coming-to-newington-plaza-receives-new-name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WATERBURY SCOOP: New restaurant coming soon to Chase Avenue</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/waterbury-scoop-new-restaurant-coming-soon-to-chase-avenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>MILFORD SCOOP: New tenants coming soon to Connecticut Post Mall!</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B13" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-new-tenants-coming-soon-to-connecticut-post-mall</t>
         </is>
